--- a/fixtures/fp-tests/5.xlsx
+++ b/fixtures/fp-tests/5.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft3248279.sharepoint.com/sites/asseticom/Shared Documents/General/04. Software Services/02. Live/C&amp;B - Equans Life Cycle Surveys/North Lanarkshire Schools/Data Imports M&amp;E/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexstanbury/Downloads/FP_Tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{9ADA6459-E753-443F-9CCD-54428F656FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D695949C-97BB-4459-8C6F-9A6DC8EA26B7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9066BA-BC05-0048-BE0C-786ED2E5317F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4E16463E-5AC6-4343-8431-EAB77F5F335F}"/>
+    <workbookView xWindow="28680" yWindow="600" windowWidth="29040" windowHeight="15840" xr2:uid="{4E16463E-5AC6-4343-8431-EAB77F5F335F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$417</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$230</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="234">
   <si>
     <t>Floor</t>
   </si>
@@ -741,564 +741,6 @@
   </si>
   <si>
     <t>GF064A - WC/SHR</t>
-  </si>
-  <si>
-    <t>Level 1</t>
-  </si>
-  <si>
-    <t>1F101 - A OFF STORE 2</t>
-  </si>
-  <si>
-    <t>1F098 - A OFF STORE 3</t>
-  </si>
-  <si>
-    <t>1F096 - A OFF STORE 4</t>
-  </si>
-  <si>
-    <t>1F085 - AREA OFFICE 1</t>
-  </si>
-  <si>
-    <t>1F054 - ART BASE</t>
-  </si>
-  <si>
-    <t>1F071 - ART CLASSROOM 1</t>
-  </si>
-  <si>
-    <t>1F072 - ART CLASSROOM 2</t>
-  </si>
-  <si>
-    <t>1F073 - ART CLASSROOM 3</t>
-  </si>
-  <si>
-    <t>1F049 - ART CLASSROOM 4</t>
-  </si>
-  <si>
-    <t>1F070 - ART STORE 1</t>
-  </si>
-  <si>
-    <t>1F051 - ART STORE 2</t>
-  </si>
-  <si>
-    <t>1F031 - ART STORE 3</t>
-  </si>
-  <si>
-    <t>1F040 - BIOLOGY STORE</t>
-  </si>
-  <si>
-    <t>1F021A - CAREERS INT ROOM</t>
-  </si>
-  <si>
-    <t>1F043 - CHEM STORE</t>
-  </si>
-  <si>
-    <t>1F033 - CHEMISTRY STORE</t>
-  </si>
-  <si>
-    <t>1F001 - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F001A - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F001B - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F001C - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F018 - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F018A - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F023 - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F028 - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F028A - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F028B - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F028C - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F028D - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F050 - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F050A - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F050B - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F050C - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F050D - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F074 - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F074A - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F074B - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F074D - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F083 - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F083A - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F083B - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F083C - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F083D - CIRCULATION</t>
-  </si>
-  <si>
-    <t>1F046 - CLEAN STORE</t>
-  </si>
-  <si>
-    <t>1F099 - CLEAN STORE 10</t>
-  </si>
-  <si>
-    <t>1F060 - CLEAN STORE 6</t>
-  </si>
-  <si>
-    <t>1F014 - CLEAN STORE 8</t>
-  </si>
-  <si>
-    <t>1F076 - CLEAN STORE 9</t>
-  </si>
-  <si>
-    <t>1F089 - COMPUTER SUITE</t>
-  </si>
-  <si>
-    <t>1F090 - COMPUTER SUITE</t>
-  </si>
-  <si>
-    <t>1F077 - CONDITIONING GYM</t>
-  </si>
-  <si>
-    <t>1F002 - CONTROL ROOM</t>
-  </si>
-  <si>
-    <t>1F017 - CUPBOARD</t>
-  </si>
-  <si>
-    <t>1F027A - CUPBOARD</t>
-  </si>
-  <si>
-    <t>1F078 - DANCE STUDIO</t>
-  </si>
-  <si>
-    <t>1F053 - DB CUPBOARD</t>
-  </si>
-  <si>
-    <t>1F069 - DB CUPBOARD</t>
-  </si>
-  <si>
-    <t>1F087 - DB CUPBOARD</t>
-  </si>
-  <si>
-    <t>1F015 - DIS WC</t>
-  </si>
-  <si>
-    <t>1F034 - DIS WC</t>
-  </si>
-  <si>
-    <t>1F075 - DIS WC</t>
-  </si>
-  <si>
-    <t>1F059 - DIS WC 7</t>
-  </si>
-  <si>
-    <t>1F024 - DIS WC 9</t>
-  </si>
-  <si>
-    <t>1F100 - DISABLED WC</t>
-  </si>
-  <si>
-    <t>1F066 - DIVISIBLE CLASSROOMS</t>
-  </si>
-  <si>
-    <t>1F066B - DIVISIBLE ROOM B</t>
-  </si>
-  <si>
-    <t>1F057 - ENG STORE</t>
-  </si>
-  <si>
-    <t>1F063 - ENGLISH CLASSROOM 1</t>
-  </si>
-  <si>
-    <t>1F064 - ENGLISH CLASSROOM 2</t>
-  </si>
-  <si>
-    <t>1F062 - ENGLISH CLASSROOM 3</t>
-  </si>
-  <si>
-    <t>1F065 - ENGLISH CLASSROOM 4</t>
-  </si>
-  <si>
-    <t>1F056 - ENGLISH CLASSROOM 5</t>
-  </si>
-  <si>
-    <t>1F055 - ENGLISH CLASSROOM 6</t>
-  </si>
-  <si>
-    <t>1F067 - ENGLISH CLASSROOM 7</t>
-  </si>
-  <si>
-    <t>1F068 - ENGLISH CLASSROOM 8</t>
-  </si>
-  <si>
-    <t>1F066D - ENGLISH DIVISIBLE CLASSROOM B</t>
-  </si>
-  <si>
-    <t>1F061 - ENGLISH STAFF BASE</t>
-  </si>
-  <si>
-    <t>1F103 - EXTERNAL PLANT AREA</t>
-  </si>
-  <si>
-    <t>1F004 - FEMALE STAFF WC</t>
-  </si>
-  <si>
-    <t>1F043A - FLAMMABLE LIQUID STORE</t>
-  </si>
-  <si>
-    <t>1F080 - FM PLANT ROOM STORE</t>
-  </si>
-  <si>
-    <t>1F091 - GP ROOM 1</t>
-  </si>
-  <si>
-    <t>1F094 - GP ROOM 2</t>
-  </si>
-  <si>
-    <t>1F039 - GREENHOUSE</t>
-  </si>
-  <si>
-    <t>1F092 - HEALTH SUITE</t>
-  </si>
-  <si>
-    <t>1F084 - INT ROOM 1</t>
-  </si>
-  <si>
-    <t>1F102 - INT ROOM 2</t>
-  </si>
-  <si>
-    <t>1F079 - INTERNAL PLANT AREA 5</t>
-  </si>
-  <si>
-    <t>1F047 - KILN ROOM</t>
-  </si>
-  <si>
-    <t>1F081 - KITCHEN VENT / AC PLANT / HEAT PLANT 4</t>
-  </si>
-  <si>
-    <t>1F021 - LIBRARY AREA</t>
-  </si>
-  <si>
-    <t>1F003 - MALE STAFF WC</t>
-  </si>
-  <si>
-    <t>2F014 - MATHS CLASSROOM 4</t>
-  </si>
-  <si>
-    <t>2F029 - MATHS CLASSROOM 7</t>
-  </si>
-  <si>
-    <t>2F030 - MATHS CLASSROOM 8</t>
-  </si>
-  <si>
-    <t>1F093 - MEDICAL ROOM</t>
-  </si>
-  <si>
-    <t>1F082 - MEETING ROOM</t>
-  </si>
-  <si>
-    <t>1F088 - MULTIPURPOSE ROOM</t>
-  </si>
-  <si>
-    <t>1F021B - OFFICE</t>
-  </si>
-  <si>
-    <t>1F027 - PHYSICS STORE</t>
-  </si>
-  <si>
-    <t>1F013 - PSHE CLASSROOM 1</t>
-  </si>
-  <si>
-    <t>1F008 - PSHE CLASSROOM 2</t>
-  </si>
-  <si>
-    <t>1F005 - PSHE STORE</t>
-  </si>
-  <si>
-    <t>1F011 - RME CLASSROOM 1</t>
-  </si>
-  <si>
-    <t>1F012 - RME CLASSROOM 1</t>
-  </si>
-  <si>
-    <t>1F010 - RME CLASSROOM 2</t>
-  </si>
-  <si>
-    <t>1F009 - RME CLASSROOM 3</t>
-  </si>
-  <si>
-    <t>1F007 - RME STAFF BASE</t>
-  </si>
-  <si>
-    <t>1F006 - RME STORE</t>
-  </si>
-  <si>
-    <t>1F029 - S6 COMMON ROOM</t>
-  </si>
-  <si>
-    <t>1F019 - SC 8</t>
-  </si>
-  <si>
-    <t>1F041 - SCIENCE LAB 1</t>
-  </si>
-  <si>
-    <t>1F026 - SCIENCE LAB 10</t>
-  </si>
-  <si>
-    <t>1F038 - SCIENCE LAB 2</t>
-  </si>
-  <si>
-    <t>1F042 - SCIENCE LAB 3</t>
-  </si>
-  <si>
-    <t>1F037 - SCIENCE LAB 4</t>
-  </si>
-  <si>
-    <t>1F044 - SCIENCE LAB 5</t>
-  </si>
-  <si>
-    <t>1F036 - SCIENCE LAB 6</t>
-  </si>
-  <si>
-    <t>1F035 - SCIENCE LAB 7</t>
-  </si>
-  <si>
-    <t>1F030 - SCIENCE LAB 8</t>
-  </si>
-  <si>
-    <t>1F025 - SCIENCE LAB 9</t>
-  </si>
-  <si>
-    <t>1F045 - SCIENCE STAFF BASE</t>
-  </si>
-  <si>
-    <t>1F016 - SECTION BOARD</t>
-  </si>
-  <si>
-    <t>1F048 - SENIOR PUPILS STUDIO</t>
-  </si>
-  <si>
-    <t>1F058 - SERVER CUPBOARD</t>
-  </si>
-  <si>
-    <t>1F020 - SERVER ROOM</t>
-  </si>
-  <si>
-    <t>1F052 - SERVER ROOM</t>
-  </si>
-  <si>
-    <t>1F086 - SERVER ROOM</t>
-  </si>
-  <si>
-    <t>2F031 - SOCIAL SUBJECTS 3</t>
-  </si>
-  <si>
-    <t>1F022 - STAFF COMMON ROOM</t>
-  </si>
-  <si>
-    <t>1F022A - STAFF KITCHEN</t>
-  </si>
-  <si>
-    <t>1F095 - STAFF ROOM</t>
-  </si>
-  <si>
-    <t>1F097 - STAFF WCS 6</t>
-  </si>
-  <si>
-    <t>1F078A - STORE</t>
-  </si>
-  <si>
-    <t>1F032 - TECHNICIAN AND PREP AREA</t>
-  </si>
-  <si>
-    <t>1F074C - VIEWING GALLERY INTO MAIN HALL</t>
-  </si>
-  <si>
-    <t>Level 2</t>
-  </si>
-  <si>
-    <t>2F001 - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F001A - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F001B - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F001C - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F001D - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F001E - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F001F - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F001G - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F001H - CIRCULATION</t>
-  </si>
-  <si>
-    <t>2F025 - CLEAN STORE 11</t>
-  </si>
-  <si>
-    <t>2F008 - CLEAN STORE 12</t>
-  </si>
-  <si>
-    <t>2F011 - DB CUPBOARD</t>
-  </si>
-  <si>
-    <t>2F027 - DB CUPBOARD</t>
-  </si>
-  <si>
-    <t>2F005 - DIS WC</t>
-  </si>
-  <si>
-    <t>2F026 - DIS WC 13</t>
-  </si>
-  <si>
-    <t>2F021 - DIVISIBLE CLASSROOMS</t>
-  </si>
-  <si>
-    <t>2F021B - DIVISIBLE ROOM B</t>
-  </si>
-  <si>
-    <t>2F021D - DIVISIBLE ROOM D</t>
-  </si>
-  <si>
-    <t>2F007 - GENERAL CLASSROOM</t>
-  </si>
-  <si>
-    <t>2F024 - GEOG STORE</t>
-  </si>
-  <si>
-    <t>2F028 - HIST STORE</t>
-  </si>
-  <si>
-    <t>2F037A - LANG REC STUDIO</t>
-  </si>
-  <si>
-    <t>2F009 - LANG STORE</t>
-  </si>
-  <si>
-    <t>2F037 - LANGUAGES RECORDING STUDIO</t>
-  </si>
-  <si>
-    <t>2F018 - MATHS CLASSROOM 1</t>
-  </si>
-  <si>
-    <t>2F019 - MATHS CLASSROOM 2</t>
-  </si>
-  <si>
-    <t>2F020 - MATHS CLASSROOM 3</t>
-  </si>
-  <si>
-    <t>2F022 - MATHS CLASSROOM 5</t>
-  </si>
-  <si>
-    <t>2F023 - MATHS CLASSROOM 6</t>
-  </si>
-  <si>
-    <t>2F017 - MATHS STAFF BASE</t>
-  </si>
-  <si>
-    <t>2F016 - MATHS STORE</t>
-  </si>
-  <si>
-    <t>2F002 - MOD LANG CLASSROOM 1</t>
-  </si>
-  <si>
-    <t>2F003 - MOD LANG CLASSROOM 2</t>
-  </si>
-  <si>
-    <t>2F040 - MOD LANG CLASSROOM 3</t>
-  </si>
-  <si>
-    <t>2F004 - MOD LANG CLASSROOM 4</t>
-  </si>
-  <si>
-    <t>2F039 - MOD LANG CLASSROOM 5</t>
-  </si>
-  <si>
-    <t>2F038 - MOD LANG CLASSROOM 6</t>
-  </si>
-  <si>
-    <t>2F006 - MOD LANG STAFF BASE</t>
-  </si>
-  <si>
-    <t>2F034 - MOD STUDIES STORE</t>
-  </si>
-  <si>
-    <t>2F041 - PLANT ROOM</t>
-  </si>
-  <si>
-    <t>2F015 - PP12</t>
-  </si>
-  <si>
-    <t>2F010 - SERVER ROOM</t>
-  </si>
-  <si>
-    <t>2F012 - SOCIAL SUBJECTS CLASS 4</t>
-  </si>
-  <si>
-    <t>2F035 - SOCIAL SUBJECTS CLASSROOM 1</t>
-  </si>
-  <si>
-    <t>2F036 - SOCIAL SUBJECTS CLASSROOM 2</t>
-  </si>
-  <si>
-    <t>2F031 - SOCIAL SUBJECTS CLASSROOM 3</t>
-  </si>
-  <si>
-    <t>2F032 - SOCIAL SUBJECTS CLASSROOM 5</t>
-  </si>
-  <si>
-    <t>2F033 - SOCIAL SUBJECTS CLASSROOM 6</t>
-  </si>
-  <si>
-    <t>2F013 - SOCIAL SUBJECTS STAFF BSE</t>
   </si>
 </sst>
 </file>
@@ -1692,14 +1134,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D460306E-570D-4BEB-8E83-BADD14129E88}">
-  <dimension ref="A1:D417"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D230"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" customWidth="1"/>
+    <col min="1" max="1" width="26.5" customWidth="1"/>
     <col min="2" max="2" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1713,7 +1155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1727,7 +1169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1741,7 +1183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1755,7 +1197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1769,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1783,7 +1225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1797,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1811,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1825,7 +1267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1839,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1853,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1867,7 +1309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1881,7 +1323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1895,7 +1337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1909,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1923,7 +1365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1937,7 +1379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1951,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1965,7 +1407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1979,7 +1421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1993,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -2007,7 +1449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -2021,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -2035,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2049,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2063,7 +1505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -2077,7 +1519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -2091,7 +1533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -2105,7 +1547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -2119,7 +1561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -2133,7 +1575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -2147,7 +1589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -2161,7 +1603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -2175,7 +1617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -2189,7 +1631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -2203,7 +1645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -2217,7 +1659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -2231,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -2245,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -2259,7 +1701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -2273,7 +1715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -2287,7 +1729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -2301,7 +1743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -2315,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -2329,7 +1771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -2343,7 +1785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -2357,7 +1799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -2371,7 +1813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -2385,7 +1827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -2399,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -2413,7 +1855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -2427,7 +1869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -2441,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -2455,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -2469,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -2483,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -2497,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -2511,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -2525,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -2539,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -2553,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -2567,7 +2009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -2581,7 +2023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -2595,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -2609,7 +2051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -2623,7 +2065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -2637,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -2651,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -2665,7 +2107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -2679,7 +2121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -2693,7 +2135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -2707,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -2721,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -2735,7 +2177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -2749,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -2763,7 +2205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -2777,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2791,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>4</v>
       </c>
@@ -2805,7 +2247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -2819,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -2833,7 +2275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2847,7 +2289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -2861,7 +2303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -2875,7 +2317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -2889,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -2903,7 +2345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -2917,7 +2359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -2931,7 +2373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -2945,7 +2387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -2959,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2973,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -2987,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -3001,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -3015,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -3029,7 +2471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -3043,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -3057,7 +2499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -3071,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -3085,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -3099,7 +2541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -3113,7 +2555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>4</v>
       </c>
@@ -3127,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -3141,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -3155,7 +2597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -3169,7 +2611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -3183,7 +2625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -3197,7 +2639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -3211,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -3225,7 +2667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -3239,7 +2681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -3253,7 +2695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -3267,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -3281,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -3295,7 +2737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -3309,7 +2751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -3323,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -3337,7 +2779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -3351,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -3365,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -3379,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -3393,7 +2835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -3407,7 +2849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -3421,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -3435,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -3449,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -3463,7 +2905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -3477,7 +2919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -3491,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -3505,7 +2947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -3519,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -3533,7 +2975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -3547,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -3561,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -3575,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -3589,7 +3031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -3603,7 +3045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -3617,7 +3059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -3631,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -3645,7 +3087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -3659,7 +3101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -3673,7 +3115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>4</v>
       </c>
@@ -3687,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>4</v>
       </c>
@@ -3701,7 +3143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -3715,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -3729,7 +3171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -3743,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -3757,7 +3199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -3771,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -3785,7 +3227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -3799,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3813,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -3827,7 +3269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -3841,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -3855,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>4</v>
       </c>
@@ -3869,7 +3311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>4</v>
       </c>
@@ -3883,7 +3325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>4</v>
       </c>
@@ -3897,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>4</v>
       </c>
@@ -3911,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -3925,7 +3367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>4</v>
       </c>
@@ -3939,7 +3381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -3953,7 +3395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -3967,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>4</v>
       </c>
@@ -3981,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>4</v>
       </c>
@@ -3995,7 +3437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>4</v>
       </c>
@@ -4009,7 +3451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>4</v>
       </c>
@@ -4023,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>4</v>
       </c>
@@ -4037,7 +3479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>4</v>
       </c>
@@ -4051,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>4</v>
       </c>
@@ -4065,7 +3507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>4</v>
       </c>
@@ -4079,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>4</v>
       </c>
@@ -4093,7 +3535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>4</v>
       </c>
@@ -4107,7 +3549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>4</v>
       </c>
@@ -4121,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>4</v>
       </c>
@@ -4135,7 +3577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>4</v>
       </c>
@@ -4149,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>4</v>
       </c>
@@ -4163,7 +3605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>4</v>
       </c>
@@ -4177,7 +3619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>4</v>
       </c>
@@ -4191,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>4</v>
       </c>
@@ -4205,7 +3647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>4</v>
       </c>
@@ -4219,7 +3661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>4</v>
       </c>
@@ -4233,7 +3675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>4</v>
       </c>
@@ -4247,7 +3689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>4</v>
       </c>
@@ -4261,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>4</v>
       </c>
@@ -4275,7 +3717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>4</v>
       </c>
@@ -4289,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>4</v>
       </c>
@@ -4303,7 +3745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>4</v>
       </c>
@@ -4317,7 +3759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>4</v>
       </c>
@@ -4331,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>4</v>
       </c>
@@ -4345,7 +3787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>4</v>
       </c>
@@ -4359,7 +3801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>4</v>
       </c>
@@ -4373,7 +3815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -4387,7 +3829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -4401,7 +3843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>4</v>
       </c>
@@ -4415,7 +3857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>4</v>
       </c>
@@ -4429,7 +3871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>4</v>
       </c>
@@ -4443,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>4</v>
       </c>
@@ -4457,7 +3899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>4</v>
       </c>
@@ -4471,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>4</v>
       </c>
@@ -4485,7 +3927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>4</v>
       </c>
@@ -4499,7 +3941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>4</v>
       </c>
@@ -4513,7 +3955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>4</v>
       </c>
@@ -4527,7 +3969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>4</v>
       </c>
@@ -4541,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>4</v>
       </c>
@@ -4555,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>4</v>
       </c>
@@ -4569,7 +4011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>4</v>
       </c>
@@ -4583,7 +4025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>4</v>
       </c>
@@ -4597,7 +4039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>4</v>
       </c>
@@ -4611,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>4</v>
       </c>
@@ -4625,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>4</v>
       </c>
@@ -4639,7 +4081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>4</v>
       </c>
@@ -4653,7 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>4</v>
       </c>
@@ -4667,7 +4109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>4</v>
       </c>
@@ -4681,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>4</v>
       </c>
@@ -4695,7 +4137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>4</v>
       </c>
@@ -4709,7 +4151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>4</v>
       </c>
@@ -4723,7 +4165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>4</v>
       </c>
@@ -4737,7 +4179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>4</v>
       </c>
@@ -4751,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>4</v>
       </c>
@@ -4765,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>4</v>
       </c>
@@ -4779,7 +4221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -4793,7 +4235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>4</v>
       </c>
@@ -4807,7 +4249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>4</v>
       </c>
@@ -4821,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>4</v>
       </c>
@@ -4835,7 +4277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>4</v>
       </c>
@@ -4849,7 +4291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>4</v>
       </c>
@@ -4863,7 +4305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>4</v>
       </c>
@@ -4877,7 +4319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>4</v>
       </c>
@@ -4891,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>4</v>
       </c>
@@ -4905,7 +4347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>4</v>
       </c>
@@ -4919,2631 +4361,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
-        <v>234</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C231">
-        <v>0</v>
-      </c>
-      <c r="D231">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>234</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C232">
-        <v>0</v>
-      </c>
-      <c r="D232">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
-        <v>234</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C233">
-        <v>0</v>
-      </c>
-      <c r="D233">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
-        <v>234</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C234">
-        <v>0</v>
-      </c>
-      <c r="D234">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
-        <v>234</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C235">
-        <v>0</v>
-      </c>
-      <c r="D235">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
-        <v>234</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C236">
-        <v>0</v>
-      </c>
-      <c r="D236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
-        <v>234</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C237">
-        <v>0</v>
-      </c>
-      <c r="D237">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
-        <v>234</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C238">
-        <v>0</v>
-      </c>
-      <c r="D238">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
-        <v>234</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C239">
-        <v>0</v>
-      </c>
-      <c r="D239">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
-        <v>234</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C240">
-        <v>0</v>
-      </c>
-      <c r="D240">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
-        <v>234</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C241">
-        <v>0</v>
-      </c>
-      <c r="D241">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
-        <v>234</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C242">
-        <v>0</v>
-      </c>
-      <c r="D242">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
-        <v>234</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C243">
-        <v>0</v>
-      </c>
-      <c r="D243">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
-        <v>234</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C244">
-        <v>0</v>
-      </c>
-      <c r="D244">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A245" t="s">
-        <v>234</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C245">
-        <v>0</v>
-      </c>
-      <c r="D245">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
-        <v>234</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="C246">
-        <v>0</v>
-      </c>
-      <c r="D246">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
-        <v>234</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C247">
-        <v>0</v>
-      </c>
-      <c r="D247">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
-        <v>234</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C248">
-        <v>0</v>
-      </c>
-      <c r="D248">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>234</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C249">
-        <v>0</v>
-      </c>
-      <c r="D249">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
-        <v>234</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C250">
-        <v>0</v>
-      </c>
-      <c r="D250">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A251" t="s">
-        <v>234</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C251">
-        <v>0</v>
-      </c>
-      <c r="D251">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A252" t="s">
-        <v>234</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C252">
-        <v>0</v>
-      </c>
-      <c r="D252">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
-        <v>234</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C253">
-        <v>0</v>
-      </c>
-      <c r="D253">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A254" t="s">
-        <v>234</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C254">
-        <v>0</v>
-      </c>
-      <c r="D254">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
-        <v>234</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C255">
-        <v>0</v>
-      </c>
-      <c r="D255">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>234</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C256">
-        <v>0</v>
-      </c>
-      <c r="D256">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
-        <v>234</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C257">
-        <v>0</v>
-      </c>
-      <c r="D257">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A258" t="s">
-        <v>234</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C258">
-        <v>0</v>
-      </c>
-      <c r="D258">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A259" t="s">
-        <v>234</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C259">
-        <v>0</v>
-      </c>
-      <c r="D259">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A260" t="s">
-        <v>234</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C260">
-        <v>0</v>
-      </c>
-      <c r="D260">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A261" t="s">
-        <v>234</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C261">
-        <v>0</v>
-      </c>
-      <c r="D261">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A262" t="s">
-        <v>234</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C262">
-        <v>0</v>
-      </c>
-      <c r="D262">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A263" t="s">
-        <v>234</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C263">
-        <v>0</v>
-      </c>
-      <c r="D263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A264" t="s">
-        <v>234</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="C264">
-        <v>0</v>
-      </c>
-      <c r="D264">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A265" t="s">
-        <v>234</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C265">
-        <v>0</v>
-      </c>
-      <c r="D265">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A266" t="s">
-        <v>234</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C266">
-        <v>0</v>
-      </c>
-      <c r="D266">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A267" t="s">
-        <v>234</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C267">
-        <v>0</v>
-      </c>
-      <c r="D267">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A268" t="s">
-        <v>234</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C268">
-        <v>0</v>
-      </c>
-      <c r="D268">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A269" t="s">
-        <v>234</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C269">
-        <v>0</v>
-      </c>
-      <c r="D269">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A270" t="s">
-        <v>234</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C270">
-        <v>0</v>
-      </c>
-      <c r="D270">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
-        <v>234</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C271">
-        <v>0</v>
-      </c>
-      <c r="D271">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A272" t="s">
-        <v>234</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C272">
-        <v>0</v>
-      </c>
-      <c r="D272">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>234</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C273">
-        <v>0</v>
-      </c>
-      <c r="D273">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>234</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C274">
-        <v>0</v>
-      </c>
-      <c r="D274">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>234</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C275">
-        <v>0</v>
-      </c>
-      <c r="D275">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
-        <v>234</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C276">
-        <v>0</v>
-      </c>
-      <c r="D276">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>234</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C277">
-        <v>0</v>
-      </c>
-      <c r="D277">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
-        <v>234</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C278">
-        <v>0</v>
-      </c>
-      <c r="D278">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
-        <v>234</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C279">
-        <v>0</v>
-      </c>
-      <c r="D279">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
-        <v>234</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C280">
-        <v>0</v>
-      </c>
-      <c r="D280">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>234</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C281">
-        <v>0</v>
-      </c>
-      <c r="D281">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>234</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C282">
-        <v>0</v>
-      </c>
-      <c r="D282">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>234</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C283">
-        <v>0</v>
-      </c>
-      <c r="D283">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>234</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C284">
-        <v>0</v>
-      </c>
-      <c r="D284">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
-        <v>234</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C285">
-        <v>0</v>
-      </c>
-      <c r="D285">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>234</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C286">
-        <v>0</v>
-      </c>
-      <c r="D286">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
-        <v>234</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C287">
-        <v>0</v>
-      </c>
-      <c r="D287">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
-        <v>234</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C288">
-        <v>0</v>
-      </c>
-      <c r="D288">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
-        <v>234</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C289">
-        <v>0</v>
-      </c>
-      <c r="D289">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
-        <v>234</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C290">
-        <v>0</v>
-      </c>
-      <c r="D290">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>234</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C291">
-        <v>0</v>
-      </c>
-      <c r="D291">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>234</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C292">
-        <v>0</v>
-      </c>
-      <c r="D292">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>234</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C293">
-        <v>0</v>
-      </c>
-      <c r="D293">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>234</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C294">
-        <v>0</v>
-      </c>
-      <c r="D294">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>234</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C295">
-        <v>0</v>
-      </c>
-      <c r="D295">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>234</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C296">
-        <v>0</v>
-      </c>
-      <c r="D296">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>234</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C297">
-        <v>0</v>
-      </c>
-      <c r="D297">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>234</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C298">
-        <v>0</v>
-      </c>
-      <c r="D298">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
-        <v>234</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="C299">
-        <v>0</v>
-      </c>
-      <c r="D299">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A300" t="s">
-        <v>234</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C300">
-        <v>0</v>
-      </c>
-      <c r="D300">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A301" t="s">
-        <v>234</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C301">
-        <v>0</v>
-      </c>
-      <c r="D301">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>234</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C302">
-        <v>0</v>
-      </c>
-      <c r="D302">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
-        <v>234</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C303">
-        <v>0</v>
-      </c>
-      <c r="D303">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>234</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C304">
-        <v>0</v>
-      </c>
-      <c r="D304">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
-        <v>234</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C305">
-        <v>0</v>
-      </c>
-      <c r="D305">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
-        <v>234</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C306">
-        <v>0</v>
-      </c>
-      <c r="D306">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A307" t="s">
-        <v>234</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C307">
-        <v>0</v>
-      </c>
-      <c r="D307">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A308" t="s">
-        <v>234</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C308">
-        <v>0</v>
-      </c>
-      <c r="D308">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
-        <v>234</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C309">
-        <v>0</v>
-      </c>
-      <c r="D309">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A310" t="s">
-        <v>234</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C310">
-        <v>0</v>
-      </c>
-      <c r="D310">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A311" t="s">
-        <v>234</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C311">
-        <v>0</v>
-      </c>
-      <c r="D311">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A312" t="s">
-        <v>234</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C312">
-        <v>0</v>
-      </c>
-      <c r="D312">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A313" t="s">
-        <v>234</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C313">
-        <v>0</v>
-      </c>
-      <c r="D313">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A314" t="s">
-        <v>234</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C314">
-        <v>0</v>
-      </c>
-      <c r="D314">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A315" t="s">
-        <v>234</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C315">
-        <v>0</v>
-      </c>
-      <c r="D315">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A316" t="s">
-        <v>234</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C316">
-        <v>0</v>
-      </c>
-      <c r="D316">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A317" t="s">
-        <v>234</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C317">
-        <v>0</v>
-      </c>
-      <c r="D317">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A318" t="s">
-        <v>234</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C318">
-        <v>0</v>
-      </c>
-      <c r="D318">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A319" t="s">
-        <v>234</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C319">
-        <v>0</v>
-      </c>
-      <c r="D319">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
-        <v>234</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C320">
-        <v>0</v>
-      </c>
-      <c r="D320">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A321" t="s">
-        <v>234</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C321">
-        <v>0</v>
-      </c>
-      <c r="D321">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A322" t="s">
-        <v>234</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C322">
-        <v>0</v>
-      </c>
-      <c r="D322">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A323" t="s">
-        <v>234</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C323">
-        <v>0</v>
-      </c>
-      <c r="D323">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A324" t="s">
-        <v>234</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C324">
-        <v>0</v>
-      </c>
-      <c r="D324">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A325" t="s">
-        <v>234</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C325">
-        <v>0</v>
-      </c>
-      <c r="D325">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A326" t="s">
-        <v>234</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C326">
-        <v>0</v>
-      </c>
-      <c r="D326">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A327" t="s">
-        <v>234</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C327">
-        <v>0</v>
-      </c>
-      <c r="D327">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A328" t="s">
-        <v>234</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C328">
-        <v>0</v>
-      </c>
-      <c r="D328">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A329" t="s">
-        <v>234</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C329">
-        <v>0</v>
-      </c>
-      <c r="D329">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A330" t="s">
-        <v>234</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C330">
-        <v>0</v>
-      </c>
-      <c r="D330">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A331" t="s">
-        <v>234</v>
-      </c>
-      <c r="B331" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C331">
-        <v>0</v>
-      </c>
-      <c r="D331">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A332" t="s">
-        <v>234</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C332">
-        <v>0</v>
-      </c>
-      <c r="D332">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A333" t="s">
-        <v>234</v>
-      </c>
-      <c r="B333" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C333">
-        <v>0</v>
-      </c>
-      <c r="D333">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A334" t="s">
-        <v>234</v>
-      </c>
-      <c r="B334" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C334">
-        <v>0</v>
-      </c>
-      <c r="D334">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A335" t="s">
-        <v>234</v>
-      </c>
-      <c r="B335" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C335">
-        <v>0</v>
-      </c>
-      <c r="D335">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A336" t="s">
-        <v>234</v>
-      </c>
-      <c r="B336" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C336">
-        <v>0</v>
-      </c>
-      <c r="D336">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A337" t="s">
-        <v>234</v>
-      </c>
-      <c r="B337" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C337">
-        <v>0</v>
-      </c>
-      <c r="D337">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A338" t="s">
-        <v>234</v>
-      </c>
-      <c r="B338" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C338">
-        <v>0</v>
-      </c>
-      <c r="D338">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A339" t="s">
-        <v>234</v>
-      </c>
-      <c r="B339" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C339">
-        <v>0</v>
-      </c>
-      <c r="D339">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A340" t="s">
-        <v>234</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C340">
-        <v>0</v>
-      </c>
-      <c r="D340">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A341" t="s">
-        <v>234</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C341">
-        <v>0</v>
-      </c>
-      <c r="D341">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
-        <v>234</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C342">
-        <v>0</v>
-      </c>
-      <c r="D342">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A343" t="s">
-        <v>234</v>
-      </c>
-      <c r="B343" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C343">
-        <v>0</v>
-      </c>
-      <c r="D343">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
-        <v>234</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C344">
-        <v>0</v>
-      </c>
-      <c r="D344">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A345" t="s">
-        <v>234</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C345">
-        <v>0</v>
-      </c>
-      <c r="D345">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A346" t="s">
-        <v>234</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C346">
-        <v>0</v>
-      </c>
-      <c r="D346">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A347" t="s">
-        <v>234</v>
-      </c>
-      <c r="B347" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C347">
-        <v>0</v>
-      </c>
-      <c r="D347">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A348" t="s">
-        <v>234</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C348">
-        <v>0</v>
-      </c>
-      <c r="D348">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
-        <v>234</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C349">
-        <v>0</v>
-      </c>
-      <c r="D349">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A350" t="s">
-        <v>234</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C350">
-        <v>0</v>
-      </c>
-      <c r="D350">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A351" t="s">
-        <v>234</v>
-      </c>
-      <c r="B351" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C351">
-        <v>0</v>
-      </c>
-      <c r="D351">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A352" t="s">
-        <v>234</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C352">
-        <v>0</v>
-      </c>
-      <c r="D352">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A353" t="s">
-        <v>234</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C353">
-        <v>0</v>
-      </c>
-      <c r="D353">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A354" t="s">
-        <v>234</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C354">
-        <v>0</v>
-      </c>
-      <c r="D354">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A355" t="s">
-        <v>234</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C355">
-        <v>0</v>
-      </c>
-      <c r="D355">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A356" t="s">
-        <v>234</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C356">
-        <v>0</v>
-      </c>
-      <c r="D356">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A357" t="s">
-        <v>234</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C357">
-        <v>0</v>
-      </c>
-      <c r="D357">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A358" t="s">
-        <v>234</v>
-      </c>
-      <c r="B358" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C358">
-        <v>0</v>
-      </c>
-      <c r="D358">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A359" t="s">
-        <v>234</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C359">
-        <v>0</v>
-      </c>
-      <c r="D359">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A360" t="s">
-        <v>234</v>
-      </c>
-      <c r="B360" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C360">
-        <v>0</v>
-      </c>
-      <c r="D360">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A361" t="s">
-        <v>234</v>
-      </c>
-      <c r="B361" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C361">
-        <v>0</v>
-      </c>
-      <c r="D361">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A362" t="s">
-        <v>234</v>
-      </c>
-      <c r="B362" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C362">
-        <v>0</v>
-      </c>
-      <c r="D362">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A363" t="s">
-        <v>234</v>
-      </c>
-      <c r="B363" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C363">
-        <v>0</v>
-      </c>
-      <c r="D363">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A364" t="s">
-        <v>234</v>
-      </c>
-      <c r="B364" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C364">
-        <v>0</v>
-      </c>
-      <c r="D364">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A365" t="s">
-        <v>234</v>
-      </c>
-      <c r="B365" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="C365">
-        <v>0</v>
-      </c>
-      <c r="D365">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A366" t="s">
-        <v>370</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C366">
-        <v>0</v>
-      </c>
-      <c r="D366">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A367" t="s">
-        <v>370</v>
-      </c>
-      <c r="B367" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C367">
-        <v>0</v>
-      </c>
-      <c r="D367">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A368" t="s">
-        <v>370</v>
-      </c>
-      <c r="B368" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C368">
-        <v>0</v>
-      </c>
-      <c r="D368">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A369" t="s">
-        <v>370</v>
-      </c>
-      <c r="B369" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C369">
-        <v>0</v>
-      </c>
-      <c r="D369">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A370" t="s">
-        <v>370</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C370">
-        <v>0</v>
-      </c>
-      <c r="D370">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A371" t="s">
-        <v>370</v>
-      </c>
-      <c r="B371" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C371">
-        <v>0</v>
-      </c>
-      <c r="D371">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A372" t="s">
-        <v>370</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C372">
-        <v>0</v>
-      </c>
-      <c r="D372">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A373" t="s">
-        <v>370</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="C373">
-        <v>0</v>
-      </c>
-      <c r="D373">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A374" t="s">
-        <v>370</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C374">
-        <v>0</v>
-      </c>
-      <c r="D374">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A375" t="s">
-        <v>370</v>
-      </c>
-      <c r="B375" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C375">
-        <v>0</v>
-      </c>
-      <c r="D375">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A376" t="s">
-        <v>370</v>
-      </c>
-      <c r="B376" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C376">
-        <v>0</v>
-      </c>
-      <c r="D376">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A377" t="s">
-        <v>370</v>
-      </c>
-      <c r="B377" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C377">
-        <v>0</v>
-      </c>
-      <c r="D377">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A378" t="s">
-        <v>370</v>
-      </c>
-      <c r="B378" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C378">
-        <v>0</v>
-      </c>
-      <c r="D378">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A379" t="s">
-        <v>370</v>
-      </c>
-      <c r="B379" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C379">
-        <v>0</v>
-      </c>
-      <c r="D379">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A380" t="s">
-        <v>370</v>
-      </c>
-      <c r="B380" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C380">
-        <v>0</v>
-      </c>
-      <c r="D380">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A381" t="s">
-        <v>370</v>
-      </c>
-      <c r="B381" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C381">
-        <v>0</v>
-      </c>
-      <c r="D381">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A382" t="s">
-        <v>370</v>
-      </c>
-      <c r="B382" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C382">
-        <v>0</v>
-      </c>
-      <c r="D382">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A383" t="s">
-        <v>370</v>
-      </c>
-      <c r="B383" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C383">
-        <v>0</v>
-      </c>
-      <c r="D383">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A384" t="s">
-        <v>370</v>
-      </c>
-      <c r="B384" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C384">
-        <v>0</v>
-      </c>
-      <c r="D384">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A385" t="s">
-        <v>370</v>
-      </c>
-      <c r="B385" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C385">
-        <v>0</v>
-      </c>
-      <c r="D385">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A386" t="s">
-        <v>370</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C386">
-        <v>0</v>
-      </c>
-      <c r="D386">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A387" t="s">
-        <v>370</v>
-      </c>
-      <c r="B387" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C387">
-        <v>0</v>
-      </c>
-      <c r="D387">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A388" t="s">
-        <v>370</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C388">
-        <v>0</v>
-      </c>
-      <c r="D388">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A389" t="s">
-        <v>370</v>
-      </c>
-      <c r="B389" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C389">
-        <v>0</v>
-      </c>
-      <c r="D389">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A390" t="s">
-        <v>370</v>
-      </c>
-      <c r="B390" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C390">
-        <v>0</v>
-      </c>
-      <c r="D390">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A391" t="s">
-        <v>370</v>
-      </c>
-      <c r="B391" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C391">
-        <v>0</v>
-      </c>
-      <c r="D391">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A392" t="s">
-        <v>370</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C392">
-        <v>0</v>
-      </c>
-      <c r="D392">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A393" t="s">
-        <v>370</v>
-      </c>
-      <c r="B393" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C393">
-        <v>0</v>
-      </c>
-      <c r="D393">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A394" t="s">
-        <v>370</v>
-      </c>
-      <c r="B394" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C394">
-        <v>0</v>
-      </c>
-      <c r="D394">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A395" t="s">
-        <v>370</v>
-      </c>
-      <c r="B395" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C395">
-        <v>0</v>
-      </c>
-      <c r="D395">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A396" t="s">
-        <v>370</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C396">
-        <v>0</v>
-      </c>
-      <c r="D396">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A397" t="s">
-        <v>370</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C397">
-        <v>0</v>
-      </c>
-      <c r="D397">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A398" t="s">
-        <v>370</v>
-      </c>
-      <c r="B398" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C398">
-        <v>0</v>
-      </c>
-      <c r="D398">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A399" t="s">
-        <v>370</v>
-      </c>
-      <c r="B399" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C399">
-        <v>0</v>
-      </c>
-      <c r="D399">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A400" t="s">
-        <v>370</v>
-      </c>
-      <c r="B400" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C400">
-        <v>0</v>
-      </c>
-      <c r="D400">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A401" t="s">
-        <v>370</v>
-      </c>
-      <c r="B401" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C401">
-        <v>0</v>
-      </c>
-      <c r="D401">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A402" t="s">
-        <v>370</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C402">
-        <v>0</v>
-      </c>
-      <c r="D402">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A403" t="s">
-        <v>370</v>
-      </c>
-      <c r="B403" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C403">
-        <v>0</v>
-      </c>
-      <c r="D403">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A404" t="s">
-        <v>370</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C404">
-        <v>0</v>
-      </c>
-      <c r="D404">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A405" t="s">
-        <v>370</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C405">
-        <v>0</v>
-      </c>
-      <c r="D405">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A406" t="s">
-        <v>370</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C406">
-        <v>0</v>
-      </c>
-      <c r="D406">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A407" t="s">
-        <v>370</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C407">
-        <v>0</v>
-      </c>
-      <c r="D407">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A408" t="s">
-        <v>370</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C408">
-        <v>0</v>
-      </c>
-      <c r="D408">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A409" t="s">
-        <v>370</v>
-      </c>
-      <c r="B409" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C409">
-        <v>0</v>
-      </c>
-      <c r="D409">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A410" t="s">
-        <v>370</v>
-      </c>
-      <c r="B410" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C410">
-        <v>0</v>
-      </c>
-      <c r="D410">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A411" t="s">
-        <v>370</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C411">
-        <v>0</v>
-      </c>
-      <c r="D411">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A412" t="s">
-        <v>370</v>
-      </c>
-      <c r="B412" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C412">
-        <v>0</v>
-      </c>
-      <c r="D412">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A413" t="s">
-        <v>370</v>
-      </c>
-      <c r="B413" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C413">
-        <v>0</v>
-      </c>
-      <c r="D413">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A414" t="s">
-        <v>370</v>
-      </c>
-      <c r="B414" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C414">
-        <v>0</v>
-      </c>
-      <c r="D414">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A415" t="s">
-        <v>370</v>
-      </c>
-      <c r="B415" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C415">
-        <v>0</v>
-      </c>
-      <c r="D415">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A416" t="s">
-        <v>370</v>
-      </c>
-      <c r="B416" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C416">
-        <v>0</v>
-      </c>
-      <c r="D416">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A417" t="s">
-        <v>370</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C417">
-        <v>0</v>
-      </c>
-      <c r="D417">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D417" xr:uid="{D460306E-570D-4BEB-8E83-BADD14129E88}"/>
+  <autoFilter ref="A1:D230" xr:uid="{D460306E-570D-4BEB-8E83-BADD14129E88}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000540BAE173F065488F2BDC1098F32ACD" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1ca55ac7cba354ca8a599c61de167ef">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="28abb233-3e57-4edf-8235-d6ecf6a0ac5a" xmlns:ns3="5db48b64-35f6-4468-8f7d-90ba9a0a6b12" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fd828bd328a808308cf08e1b855890b0" ns2:_="" ns3:_="">
     <xsd:import namespace="28abb233-3e57-4edf-8235-d6ecf6a0ac5a"/>
@@ -7790,15 +4623,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7812,13 +4636,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF2EBE90-D48D-41AF-A03A-F8B5CBF99CB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6E04DD-89D9-4B51-B1EC-4FBA0765540F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6E04DD-89D9-4B51-B1EC-4FBA0765540F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF2EBE90-D48D-41AF-A03A-F8B5CBF99CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="28abb233-3e57-4edf-8235-d6ecf6a0ac5a"/>
+    <ds:schemaRef ds:uri="5db48b64-35f6-4468-8f7d-90ba9a0a6b12"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32C80F12-890E-4E85-8317-4A317065F4C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32C80F12-890E-4E85-8317-4A317065F4C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5db48b64-35f6-4468-8f7d-90ba9a0a6b12"/>
+    <ds:schemaRef ds:uri="28abb233-3e57-4edf-8235-d6ecf6a0ac5a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>